--- a/18.11.25/string task.xlsx
+++ b/18.11.25/string task.xlsx
@@ -2199,7 +2199,7 @@
         <v>49</v>
       </c>
       <c r="M7" t="str">
-        <f>RIGHT(C7,11)</f>
+        <f>_xlfn.TEXTAFTER(C7,"@")</f>
         <v>hotmail.com</v>
       </c>
     </row>
@@ -2232,7 +2232,7 @@
         <v>56</v>
       </c>
       <c r="M8" t="str">
-        <f>LEFT(C8,10)</f>
+        <f>_xlfn.TEXTBEFORE(C8,"@")</f>
         <v>deepakm123</v>
       </c>
     </row>
@@ -2331,8 +2331,8 @@
         <v>74</v>
       </c>
       <c r="M11" t="str">
-        <f>_xlfn.CONCAT(B11,E11)</f>
-        <v>Saranya KSalem</v>
+        <f>_xlfn.CONCAT(_xlfn.TEXTBEFORE(B11," "),E11)</f>
+        <v>SaranyaSalem</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -2796,8 +2796,8 @@
         <v>158</v>
       </c>
       <c r="M25" t="str">
-        <f>SUBSTITUTE(F25,"EMP","")</f>
-        <v>-ERD-2244</v>
+        <f>SUBSTITUTE(F25,"EMP-","")</f>
+        <v>ERD-2244</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -3060,7 +3060,7 @@
         <v>Kavin GEMP-MDU-1199</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:13">
       <c r="A34">
         <v>33</v>
       </c>
@@ -3088,8 +3088,12 @@
       <c r="J34" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="35" spans="1:10">
+      <c r="M34" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F34,"0",""),"1",""),"2",""),"3",""),"4",""),"5",""),"6",""),"7",""),"8",""),"9","")</f>
+        <v>EMP-ERD-</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
       <c r="A35">
         <v>34</v>
       </c>
@@ -3116,6 +3120,10 @@
       </c>
       <c r="J35" t="s">
         <v>217</v>
+      </c>
+      <c r="M35" t="str">
+        <f>RIGHT(F35,4)</f>
+        <v>4432</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -3151,7 +3159,7 @@
         <v>True</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:13">
       <c r="A37">
         <v>36</v>
       </c>
@@ -3179,8 +3187,12 @@
       <c r="J37" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="38" spans="1:10">
+      <c r="M37" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(C37,"@",""),".","")</f>
+        <v>sidrofficecom</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13">
       <c r="A38">
         <v>37</v>
       </c>
@@ -3207,6 +3219,10 @@
       </c>
       <c r="J38" t="s">
         <v>235</v>
+      </c>
+      <c r="M38" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(D38,"-",""),"+","")</f>
+        <v>9345609871</v>
       </c>
     </row>
     <row r="39" spans="1:13">
